--- a/stories/arbres/ATOM-JEU.BAL.001-08.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Baptiste est dans le jardin. Papa montre l'espace du jeu. L'herbe est courte. Baptiste a le ballon. Papa dit : on se passe le ballon. Chacun a un tour. Baptiste passe le ballon. Papa le renvoie. C'est le tour de Baptiste. Parce qu'il reste dans l'espace du jeu, le ballon reste près. Ils jouent. Baptiste attend son tour. Il passe encore. Le ballon est doux. Papa sourit.</t>
+          <t>Baptiste est dans le jardin. Papa montre l'espace du jeu. L'herbe est courte. Baptiste a le ballon. On se passe le ballon. Chacun a un tour. Baptiste passe le ballon. Papa le renvoie. C'est le tour de Baptiste. Parce qu'il reste dans l'espace du jeu, le ballon reste près. Ils jouent. Baptiste attend son tour. Il passe encore. Le ballon est doux. Papa sourit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Baptiste est dans le jardin. Papa montre l'espace du jeu. L'herbe est courte. Baptiste a le ballon.
+papa|On se passe le ballon. Chacun a un tour.
+narrateur|Baptiste passe le ballon. Papa le renvoie. C'est le tour de Baptiste. Parce qu'il reste dans l'espace du jeu, le ballon reste près. Ils jouent. Baptiste attend son tour. Il passe encore. Le ballon est doux. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Baptiste a le ballon. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Baptiste a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Baptiste pose le ballon. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-08.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Baptiste passe le ballon. Papa le renvoie. C'est le tour de Baptiste. Parce qu'il reste dans l'espace du jeu, le ballon reste près. Ils jouent. Baptiste attend son tour. Il passe encore. Le ballon est doux. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1505,7 @@
           <t>narrateur|Baptiste a le ballon. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1677,7 @@
           <t>narrateur|Baptiste a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1841,7 @@
           <t>narrateur|Baptiste pose le ballon. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.BAL.001-08.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Baptiste passe le ballon</t>
+          <t>Raphaël passe le ballon</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une abeille se pose sur une fleur jaune. Raphaël et papa se passent le ballon dans l'espace du jeu.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Baptiste est dans le jardin. Papa montre l'espace du jeu. L'herbe est courte. Baptiste a le ballon. On se passe le ballon. Chacun a un tour. Baptiste passe le ballon. Papa le renvoie. C'est le tour de Baptiste. Parce qu'il reste dans l'espace du jeu, le ballon reste près. Ils jouent. Baptiste attend son tour. Il passe encore. Le ballon est doux. Papa sourit.</t>
+          <t>Une abeille se pose sur une fleur jaune. La fleur penche un tout petit peu. Le tuyau du jardin est chaud. Il sent le caoutchouc et l'eau. Derrière la haie, des voix d'enfants. L'herbe est courte et sèche. Raphaël, tu as vu l'abeille ? Oui. Elle est sur la fleur. En ce moment, Raphaël marche dans le jardin. Ses chaussettes glissent un peu dans l'herbe. Voici l'espace du jeu. Papa montre l'espace entre deux seaux. Raphaël a le ballon. Le ballon est doux sous les doigts. On se passe le ballon. Chacun a un tour. Raphaël passe le ballon. Papa le renvoie tout doucement. C'est le tour de Raphaël. Il reste dans l'espace du jeu. Le ballon reste près. Ils jouent. Le ballon va et vient. Raphaël attend son tour. Il passe encore. Il est doux, le ballon. Oui. Et tu restes dans l'espace. Bravo. Tu as attendu. L'abeille change de fleur. Raphaël la regarde, puis il attend. C'est ton tour. Il passe le ballon à papa. Bien joué. J'attrape. Papa passe. Raphaël attrape. Raphaël reste dans l'espace du jeu. Encore un tour ? Oui. Chacun a un tour. Ils se passent le ballon encore. Tu as fait du bon travail. La fleur jaune se redresse. Un seau penche un peu dans l'herbe. On reste entre les deux seaux. C'est l'espace du jeu. Oui. Tu passes. Tu attends. Raphaël attend. Puis il passe. Bravo, Raphaël. L'abeille s'envole vers la haie. Raphaël suit des yeux, puis il attend. Le ballon est pour toi. Raphaël passe le ballon. Bravo. Tu as attendu ton tour. L'herbe sèche gratte un peu. Ça pique un tout petit peu. Oui. On reste dans l'espace du jeu. Les deux seaux marquent l'espace. Raphaël reste entre les seaux. On se passe le ballon. Chacun a un tour. Papa passe. Raphaël attrape. Raphaël passe. Merci. L'abeille est partie. Oui. Et toi, tu as bien joué. Une fleur jaune se balance encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,68 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Baptiste est dans le jardin. Papa montre l'espace du jeu. L'herbe est courte. Baptiste a le ballon.
+          <t>narrateur|Une abeille se pose sur une fleur jaune.
+narrateur|La fleur penche un tout petit peu.
+narrateur|Le tuyau du jardin est chaud.
+narrateur|Il sent le caoutchouc et l'eau.
+narrateur|Derrière la haie, des voix d'enfants.
+narrateur|L'herbe est courte et sèche.
+papa|Raphaël, tu as vu l'abeille ?
+enfant-m|Oui. Elle est sur la fleur.
+narrateur|En ce moment, Raphaël marche dans le jardin.
+narrateur|Ses chaussettes glissent un peu dans l'herbe.
+papa|Voici l'espace du jeu.
+narrateur|Papa montre l'espace entre deux seaux.
+narrateur|Raphaël a le ballon.
+narrateur|Le ballon est doux sous les doigts.
+papa|On se passe le ballon.
+papa|Chacun a un tour.
+narrateur|Raphaël passe le ballon.
+narrateur|Papa le renvoie tout doucement.
+papa|C'est le tour de Raphaël.
+narrateur|Il reste dans l'espace du jeu.
+narrateur|Le ballon reste près.
+narrateur|Ils jouent. Le ballon va et vient.
+narrateur|Raphaël attend son tour.
+narrateur|Il passe encore.
+enfant-m|Il est doux, le ballon.
+papa|Oui. Et tu restes dans l'espace.
+papa|Bravo. Tu as attendu.
+narrateur|L'abeille change de fleur.
+narrateur|Raphaël la regarde, puis il attend.
+papa|C'est ton tour.
+narrateur|Il passe le ballon à papa.
+papa|Bien joué. J'attrape.
+narrateur|Papa passe. Raphaël attrape.
+narrateur|Raphaël reste dans l'espace du jeu.
+enfant-m|Encore un tour ?
+papa|Oui. Chacun a un tour.
+narrateur|Ils se passent le ballon encore.
+papa|Tu as fait du bon travail.
+narrateur|La fleur jaune se redresse.
+narrateur|Un seau penche un peu dans l'herbe.
+papa|On reste entre les deux seaux.
+enfant-m|C'est l'espace du jeu.
+papa|Oui. Tu passes. Tu attends.
+narrateur|Raphaël attend. Puis il passe.
+papa|Bravo, Raphaël.
+narrateur|L'abeille s'envole vers la haie.
+narrateur|Raphaël suit des yeux, puis il attend.
+papa|Le ballon est pour toi.
+narrateur|Raphaël passe le ballon.
+papa|Bravo. Tu as attendu ton tour.
+narrateur|L'herbe sèche gratte un peu.
+enfant-m|Ça pique un tout petit peu.
+papa|Oui. On reste dans l'espace du jeu.
+narrateur|Les deux seaux marquent l'espace.
+narrateur|Raphaël reste entre les seaux.
 papa|On se passe le ballon. Chacun a un tour.
-narrateur|Baptiste passe le ballon. Papa le renvoie. C'est le tour de Baptiste. Parce qu'il reste dans l'espace du jeu, le ballon reste près. Ils jouent. Baptiste attend son tour. Il passe encore. Le ballon est doux. Papa sourit.</t>
+narrateur|Papa passe. Raphaël attrape.
+narrateur|Raphaël passe.
+papa|Merci.
+enfant-m|L'abeille est partie.
+papa|Oui. Et toi, tu as bien joué.
+narrateur|Une fleur jaune se balance encore.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1346,7 +1417,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Baptiste a le ballon. Que fait-il ?</t>
+          <t>Raphaël a le ballon. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,10 +1573,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Baptiste a le ballon. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Raphaël a le ballon.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,7 +1601,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Baptiste a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
+          <t>Raphaël a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu. Tu as passé. Tu as attendu. Tu es resté dans l'espace. Chacun a un tour. Oui. Bravo, Raphaël. La fleur jaune se balance un peu. Le tuyau reste chaud dans l'herbe.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,10 +1745,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Baptiste a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Raphaël a passé le ballon.
+narrateur|Il a attendu son tour.
+narrateur|Il est resté dans l'espace du jeu.
+papa|Tu as passé. Tu as attendu.
+papa|Tu es resté dans l'espace.
+enfant-m|Chacun a un tour.
+papa|Oui. Bravo, Raphaël.
+narrateur|La fleur jaune se balance un peu.
+narrateur|Le tuyau reste chaud dans l'herbe.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1702,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Baptiste pose le ballon. Papa range le seau.</t>
+          <t>Raphaël pose le ballon. Papa range le seau. Tu as fini de jouer ? Oui, papa. Bravo. On rentre. L'herbe gratte un peu les chevilles. Ils rentrent. L'abeille n'est plus sur la fleur.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,10 +1916,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Baptiste pose le ballon. Papa range le seau.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Raphaël pose le ballon.
+narrateur|Papa range le seau.
+papa|Tu as fini de jouer ?
+enfant-m|Oui, papa.
+papa|Bravo. On rentre.
+narrateur|L'herbe gratte un peu les chevilles.
+narrateur|Ils rentrent.
+narrateur|L'abeille n'est plus sur la fleur.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1866,7 +1950,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le ballon est posé près de la porte. Raphaël a passé. Il a attendu. Bravo, Raphaël. Tu as bien joué. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,10 +2090,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le ballon est posé près de la porte.
+narrateur|Raphaël a passé. Il a attendu.
+papa|Bravo, Raphaël. Tu as bien joué.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2152,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-08.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-08.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une abeille se pose sur une fleur jaune. La fleur penche un tout petit peu. Le tuyau du jardin est chaud. Il sent le caoutchouc et l'eau. Derrière la haie, des voix d'enfants. L'herbe est courte et sèche. Raphaël, tu as vu l'abeille ? Oui. Elle est sur la fleur. En ce moment, Raphaël marche dans le jardin. Ses chaussettes glissent un peu dans l'herbe. Voici l'espace du jeu. Papa montre l'espace entre deux seaux. Raphaël a le ballon. Le ballon est doux sous les doigts. On se passe le ballon. Chacun a un tour. Raphaël passe le ballon. Papa le renvoie tout doucement. C'est le tour de Raphaël. Il reste dans l'espace du jeu. Le ballon reste près. Ils jouent. Le ballon va et vient. Raphaël attend son tour. Il passe encore. Il est doux, le ballon. Oui. Et tu restes dans l'espace. Bravo. Tu as attendu. L'abeille change de fleur. Raphaël la regarde, puis il attend. C'est ton tour. Il passe le ballon à papa. Bien joué. J'attrape. Papa passe. Raphaël attrape. Raphaël reste dans l'espace du jeu. Encore un tour ? Oui. Chacun a un tour. Ils se passent le ballon encore. Tu as fait du bon travail. La fleur jaune se redresse. Un seau penche un peu dans l'herbe. On reste entre les deux seaux. C'est l'espace du jeu. Oui. Tu passes. Tu attends. Raphaël attend. Puis il passe. Bravo, Raphaël. L'abeille s'envole vers la haie. Raphaël suit des yeux, puis il attend. Le ballon est pour toi. Raphaël passe le ballon. Bravo. Tu as attendu ton tour. L'herbe sèche gratte un peu. Ça pique un tout petit peu. Oui. On reste dans l'espace du jeu. Les deux seaux marquent l'espace. Raphaël reste entre les seaux. On se passe le ballon. Chacun a un tour. Papa passe. Raphaël attrape. Raphaël passe. Merci. L'abeille est partie. Oui. Et toi, tu as bien joué. Une fleur jaune se balance encore.</t>
+          <t>Une abeille se pose sur une fleur jaune. La fleur penche un tout petit peu. Le tuyau du jardin est chaud. Il sent le caoutchouc et l'eau. Derrière la haie, des voix d'enfants. L'herbe est courte et sèche. Raphaël, tu as vu l'abeille ? Oui. Elle est sur la fleur. En ce moment, Raphaël marche dans le jardin. Ses chaussettes glissent un peu dans l'herbe. Voici l'espace du jeu. Papa montre l'espace entre deux seaux. Raphaël a le ballon. Le ballon est doux sous les doigts. On se passe le ballon. Chacun a un tour. Raphaël passe le ballon. Papa le renvoie tout doucement. C'est le tour de Raphaël. Il reste dans l'espace du jeu. Le ballon reste près. Ils jouent. Le ballon va et vient. Raphaël attend son tour. Il passe encore. Il est doux, le ballon. Oui. Et tu restes dans l'espace. Bravo. Tu as attendu. L'abeille change de fleur. Raphaël la regarde, puis il attend. C'est ton tour. Il passe le ballon à papa. Bien joué. J'attrape. Papa passe. Raphaël attrape. Raphaël reste dans l'espace du jeu. Encore un tour ? Oui. Chacun a un tour. Ils se passent le ballon encore. La fleur jaune se redresse. Un seau penche un peu dans l'herbe. On reste entre les deux seaux. C'est l'espace du jeu. Oui. Tu passes. Tu attends. Raphaël attend. Puis il passe. Bravo, Raphaël. L'abeille s'envole vers la haie. Raphaël suit des yeux, puis il attend. Le ballon est pour toi. Raphaël passe le ballon. Bravo. Tu as attendu ton tour. L'herbe sèche gratte un peu. Ça pique un tout petit peu. Oui. On reste dans l'espace du jeu. Les deux seaux marquent l'espace. Raphaël reste entre les seaux. On se passe le ballon. Chacun a un tour. Papa passe. Raphaël attrape. Raphaël passe. Merci. L'abeille est partie. Oui. Et toi, tu as bien joué. Une fleur jaune se balance encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Baptiste est dans le jardin. Papa montre l'espace du jeu. L'herbe est courte. Baptiste a le ballon. Papa dit : on se passe le ballon. Chacun a un &lt;emphasis level="moderate"&gt;tour&lt;/emphasis&gt;. Baptiste passe le ballon. Papa le renvoie. C'est le tour de Baptiste. Parce qu'il reste dans l'espace du jeu, le ballon reste près. Ils jouent. Baptiste attend son tour. Il passe encore. Le ballon est doux. Papa sourit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une abeille se pose sur une fleur jaune. La fleur penche un tout petit peu. Le tuyau du jardin est chaud. Il sent le caoutchouc et l'eau. Derrière la haie, des voix d'enfants. L'herbe est courte et sèche. Raphaël, tu as vu l'abeille ? Oui. Elle est sur la fleur. En ce moment, Raphaël marche dans le jardin. Ses chaussettes glissent un peu dans l'herbe. Voici l'espace du jeu. Papa montre l'espace entre deux seaux. Raphaël a le ballon. Le ballon est doux sous les doigts. On se passe le ballon. Chacun a un tour. Raphaël passe le ballon. Papa le renvoie tout doucement. C'est le tour de Raphaël. Il reste dans l'espace du jeu. Le ballon reste près. Ils jouent. Le ballon va et vient. Raphaël attend son tour. Il passe encore. Il est doux, le ballon. Oui. Et tu restes dans l'espace. Bravo. Tu as attendu. L'abeille change de fleur. Raphaël la regarde, puis il attend. C'est ton tour. Il passe le ballon à papa. Bien joué. J'attrape. Papa passe. Raphaël attrape. Raphaël reste dans l'espace du jeu. Encore un tour ? Oui. Chacun a un tour. Ils se passent le ballon encore. La fleur jaune se redresse. Un seau penche un peu dans l'herbe. On reste entre les deux seaux. C'est l'espace du jeu. Oui. Tu passes. Tu attends. Raphaël attend. Puis il passe. Bravo, Raphaël. L'abeille s'envole vers la haie. Raphaël suit des yeux, puis il attend. Le ballon est pour toi. Raphaël passe le ballon. Bravo. Tu as attendu ton tour. L'herbe sèche gratte un peu. Ça pique un tout petit peu. Oui. On reste dans l'espace du jeu. Les deux seaux marquent l'espace. Raphaël reste entre les seaux. On se passe le ballon. Chacun a un tour. Papa passe. Raphaël attrape. Raphaël passe. Merci. L'abeille est partie. Oui. Et toi, tu as bien joué. Une fleur jaune se balance encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1361,7 +1361,6 @@
 enfant-m|Encore un tour ?
 papa|Oui. Chacun a un tour.
 narrateur|Ils se passent le ballon encore.
-papa|Tu as fait du bon travail.
 narrateur|La fleur jaune se redresse.
 narrateur|Un seau penche un peu dans l'herbe.
 papa|On reste entre les deux seaux.
@@ -1422,7 +1421,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Baptiste a le ballon. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a le ballon. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1606,7 +1605,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Baptiste a passé le ballon. Il a attendu son &lt;emphasis level="moderate"&gt;tour&lt;/emphasis&gt;. Il est resté dans l'espace du jeu.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu. Tu as passé. Tu as attendu. Tu es resté dans l'espace. Chacun a un tour. Oui. Bravo, Raphaël. La fleur jaune se balance un peu. Le tuyau reste chaud dans l'herbe.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1785,7 +1784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Baptiste pose le ballon. Papa range le seau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël pose le ballon. Papa range le seau. Tu as fini de jouer ? Oui, papa. Bravo. On rentre. L'herbe gratte un peu les chevilles. Ils rentrent. L'abeille n'est plus sur la fleur.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1950,12 +1949,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le ballon est posé près de la porte. Raphaël a passé. Il a attendu. Bravo, Raphaël. Tu as bien joué. L'histoire est finie.</t>
+          <t>Le ballon est posé près de la porte. Raphaël a passé. Il a attendu. Bravo, Raphaël. Tu as bien joué.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le ballon est posé près de la porte. Raphaël a passé. Il a attendu. Bravo, Raphaël. Tu as bien joué.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2092,8 +2091,7 @@
         <is>
           <t>narrateur|Le ballon est posé près de la porte.
 narrateur|Raphaël a passé. Il a attendu.
-papa|Bravo, Raphaël. Tu as bien joué.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Raphaël. Tu as bien joué.</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2159,6 +2157,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-08.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-08.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Baptiste, papa</t>
+          <t>Raphaël, papa</t>
         </is>
       </c>
     </row>
